--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/aggregation-conformance.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/aggregation-conformance.xlsx
@@ -8,41 +8,42 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB76FE33-5CBF-4145-BBFE-DA89713F66CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B882E7FC-DB9E-4B3F-8E0B-DB3347118C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{8DD4ED6A-0E06-4D82-B66D-B7141252667D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{3E1EE5EB-53F1-408B-A92B-0651D5ADE064}"/>
   </bookViews>
   <sheets>
-    <sheet name="ErrorGroups" sheetId="15" r:id="rId1"/>
-    <sheet name="ErrorSource" sheetId="14" r:id="rId2"/>
-    <sheet name="VarianceP" sheetId="13" r:id="rId3"/>
-    <sheet name="Variance" sheetId="12" r:id="rId4"/>
-    <sheet name="StandardDeviationP" sheetId="11" r:id="rId5"/>
-    <sheet name="StandardDeviation" sheetId="10" r:id="rId6"/>
-    <sheet name="Product" sheetId="9" r:id="rId7"/>
-    <sheet name="Maximum" sheetId="8" r:id="rId8"/>
-    <sheet name="Minimum" sheetId="7" r:id="rId9"/>
-    <sheet name="Average" sheetId="6" r:id="rId10"/>
-    <sheet name="CountNumbers" sheetId="5" r:id="rId11"/>
-    <sheet name="Count" sheetId="4" r:id="rId12"/>
-    <sheet name="Sum" sheetId="3" r:id="rId13"/>
-    <sheet name="Lookups" sheetId="2" r:id="rId14"/>
-    <sheet name="Source" sheetId="1" r:id="rId15"/>
+    <sheet name="LookupEdges" sheetId="16" r:id="rId1"/>
+    <sheet name="ErrorGroups" sheetId="15" r:id="rId2"/>
+    <sheet name="ErrorSource" sheetId="14" r:id="rId3"/>
+    <sheet name="VarianceP" sheetId="13" r:id="rId4"/>
+    <sheet name="Variance" sheetId="12" r:id="rId5"/>
+    <sheet name="StandardDeviationP" sheetId="11" r:id="rId6"/>
+    <sheet name="StandardDeviation" sheetId="10" r:id="rId7"/>
+    <sheet name="Product" sheetId="9" r:id="rId8"/>
+    <sheet name="Maximum" sheetId="8" r:id="rId9"/>
+    <sheet name="Minimum" sheetId="7" r:id="rId10"/>
+    <sheet name="Average" sheetId="6" r:id="rId11"/>
+    <sheet name="CountNumbers" sheetId="5" r:id="rId12"/>
+    <sheet name="Count" sheetId="4" r:id="rId13"/>
+    <sheet name="Sum" sheetId="3" r:id="rId14"/>
+    <sheet name="Lookups" sheetId="2" r:id="rId15"/>
+    <sheet name="Source" sheetId="1" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId16"/>
-    <pivotCache cacheId="19" r:id="rId17"/>
-    <pivotCache cacheId="29" r:id="rId18"/>
-    <pivotCache cacheId="39" r:id="rId19"/>
-    <pivotCache cacheId="49" r:id="rId20"/>
-    <pivotCache cacheId="59" r:id="rId21"/>
-    <pivotCache cacheId="69" r:id="rId22"/>
-    <pivotCache cacheId="79" r:id="rId23"/>
-    <pivotCache cacheId="89" r:id="rId24"/>
-    <pivotCache cacheId="99" r:id="rId25"/>
-    <pivotCache cacheId="109" r:id="rId26"/>
-    <pivotCache cacheId="117" r:id="rId27"/>
+    <pivotCache cacheId="9" r:id="rId17"/>
+    <pivotCache cacheId="19" r:id="rId18"/>
+    <pivotCache cacheId="29" r:id="rId19"/>
+    <pivotCache cacheId="39" r:id="rId20"/>
+    <pivotCache cacheId="49" r:id="rId21"/>
+    <pivotCache cacheId="59" r:id="rId22"/>
+    <pivotCache cacheId="69" r:id="rId23"/>
+    <pivotCache cacheId="79" r:id="rId24"/>
+    <pivotCache cacheId="89" r:id="rId25"/>
+    <pivotCache cacheId="99" r:id="rId26"/>
+    <pivotCache cacheId="109" r:id="rId27"/>
+    <pivotCache cacheId="117" r:id="rId28"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -251,7 +252,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642323495369" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{EC654CDF-298B-4A32-8D2D-9AF44B07CA56}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658789814814" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{213C3A12-7F95-4031-AB2F-0DFD676DA18A}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -285,7 +286,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642349768517" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{CEB37763-E135-4EE0-A1AA-C1D442C3B240}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.65879710648" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{23A19AC0-19E5-48C4-A05D-8334BDD0D15F}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -319,7 +320,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642352893519" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{080FBA70-FC61-4B78-AC00-190691DB8BF1}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658797916665" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{9AE02201-051C-458C-AB4D-1C4C5074300A}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -353,7 +354,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.64236273148" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{8E6157AA-EDB4-497D-9C85-20D4462F418C}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658802662037" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{AC9CCD48-357C-4DDD-85DB-5F3D34C5C6E2}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="ErrorSource"/>
   </cacheSource>
@@ -381,7 +382,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642326851848" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{C17783FA-50E3-472C-B617-C60106D8184D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658790856483" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{2BC03678-FBB0-47E9-ADC6-5CC3791277A4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -415,7 +416,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642329745373" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{95157866-F6E9-455C-83CC-124D15F37CB3}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658791550923" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{6FF4B22B-F1AF-45E2-AAE1-6C24335E59C7}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -449,7 +450,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642332523152" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{AD7992FD-5447-4ADF-97EB-1462B64E9061}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658792245369" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{E60A7CEF-2149-4B98-82EF-EF457C42E97A}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -483,7 +484,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642335416669" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{CFE84EF1-715D-4BD7-A5A7-CEA8CA306733}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658792939816" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{7A645670-8CF9-4605-8669-6A848EF6173A}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -517,7 +518,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642338078702" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{445239FA-8434-4401-B32A-F433034F75EE}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658793750001" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{9052A462-4DC9-4DFA-AF7A-C92F86F25761}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -551,7 +552,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642340972219" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{DDBF7E09-4A21-4299-AE72-BB35F912AC66}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658794675925" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{49F60F01-5BED-4AAE-BA95-36CC68C82EE6}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -585,7 +586,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642343865744" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{B8C14259-D530-46C8-A41A-9EB7ED655BD5}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.65879548611" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{274F422E-813F-411A-B03C-F9EC99F1C609}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -619,7 +620,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.642346643515" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{CC1C288F-14DE-48E3-BAD4-49FFC591EF2B}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658796296295" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{4BA254D4-7DA4-441F-9D62-2CDB6281980A}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -1269,7 +1270,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45B3ED12-EB97-4033-BA36-B370326C5347}" name="PivotErrorGroups" cacheId="117" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37E92055-9170-482B-93D5-D9DE7ECBA4A6}" name="PivotErrorGroups" cacheId="117" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:L8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
@@ -1375,7 +1376,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57841FC6-126A-4FDB-96E9-559D0CC749E4}" name="PivotCountNumbers" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6058C8B8-9986-4DF3-AAD6-DCEC37425A1E}" name="PivotCountNumbers" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1442,7 +1443,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{993FE003-897D-467C-97FA-910C8F5A041A}" name="PivotCount" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39850292-163F-47AE-9C58-9C5046602472}" name="PivotCount" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1509,7 +1510,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7AB691EB-639A-4E9D-9D71-49E4618B7942}" name="PivotSum" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{97D9914D-9FF5-431C-B8BC-9831E2DA7E3F}" name="PivotSum" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1576,7 +1577,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{97924DC0-818E-4B32-9259-9B0A3E7380A4}" name="PivotVarianceP" cacheId="109" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3BA77F5B-15AA-489B-88A1-5CD68AE0A747}" name="PivotVarianceP" cacheId="109" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1643,7 +1644,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5EE6788-4E48-4756-826C-D22DE0A32B11}" name="PivotVariance" cacheId="99" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D1D96C1-37EB-4E05-BCBD-0BC067E9701D}" name="PivotVariance" cacheId="99" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1710,7 +1711,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7906F1A7-B461-4743-9CFE-D92587BF52B4}" name="PivotStandardDeviationP" cacheId="89" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04319975-3807-4EA2-9C67-344EA160698E}" name="PivotStandardDeviationP" cacheId="89" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1777,7 +1778,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{07D4F9BC-356E-4931-B14F-7D7261639FE8}" name="PivotStandardDeviation" cacheId="79" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FAFD2AF-BF41-4D45-9FE0-68E750742265}" name="PivotStandardDeviation" cacheId="79" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1844,7 +1845,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8001C05E-FB9A-4420-B8D2-2560DF194749}" name="PivotProduct" cacheId="69" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3FCF7C71-FD19-4E1B-922A-BC0071CDDE02}" name="PivotProduct" cacheId="69" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1911,7 +1912,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4A81ADC2-E055-40CC-8C89-6791B5DEF2F1}" name="PivotMaximum" cacheId="59" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C227D33-B72B-4E23-AD49-B0EA618FCFB1}" name="PivotMaximum" cacheId="59" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1978,7 +1979,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A9F2499-03E1-4BE2-B062-9DEE88C54F1D}" name="PivotMinimum" cacheId="49" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2AB65852-B67F-4B84-ACCF-8BE183442F56}" name="PivotMinimum" cacheId="49" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -2045,7 +2046,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11ED442A-AC26-488A-AA05-4D24DAC24685}" name="PivotAverage" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DD63A28E-3CFC-4E82-9D1C-513961A59241}" name="PivotAverage" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -2427,7 +2428,2211 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{476AD8F6-62AB-480C-97D1-5109E2E2FCDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6ABF11-90F5-4A64-85C3-47D415AD811C}">
+  <dimension ref="A1:A22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","West","Product","A")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <f>GETPIVOTDATA("Amount",Sum!A1)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="e">
+        <f>GETPIVOTDATA("Count",ErrorGroups!A1)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="e">
+        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <f>GETPIVOTDATA("Metric",Sum!B4,"Region","North")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <f>GETPIVOTDATA("Metric",Sum!A1:D6,"Product","A")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="e">
+        <f>GETPIVOTDATA("Metric",Sum!Z1)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","North","Region","North")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="e">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","North","Region","South")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","north")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="e">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"notafield","A")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="e">
+        <f>GETPIVOTDATA("missing",Sum!A1)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <f>IFERROR(GETPIVOTDATA("Metric",Sum!Z1),77)</f>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region",Source!A2)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","West","Product","B")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Product","a")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Literal")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Literal")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="e">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Product",1)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D103399-47F3-47D2-9A1D-016145D8F614}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>-2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>-2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8914D4A-8D2B-45F9-BA2F-15240B271009}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3">
+        <v>9.3333333333333339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="C6" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>9.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ECD3F9C-B9DF-4218-AA76-DE9F06117257}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DBDC9F4-3908-4676-9356-9D0C9B26F64E}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155D7EB4-54D0-46F8-BB19-439B4F7B4755}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3">
+        <v>35</v>
+      </c>
+      <c r="D6" s="3">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49DA6248-ED1D-40D3-B4CB-4907CCE5B963}">
+  <dimension ref="A1:B165"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1">
+        <f>GETPIVOTDATA("Metric",Sum!A1)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","North")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","South")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Product","A")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Product","B")</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","North","Product","A")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","South","Product","B")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="e">
+        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <f>GETPIVOTDATA("Metric",Count!A1)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <f>GETPIVOTDATA("Metric",Count!A1,"Region","North")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <f>GETPIVOTDATA("Metric",Count!A1,"Region","South")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <f>GETPIVOTDATA("Metric",Count!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <f>GETPIVOTDATA("Metric",Count!A1,"Product","A")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <f>GETPIVOTDATA("Metric",Count!A1,"Product","B")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <f>GETPIVOTDATA("Metric",Count!A1,"Region","North","Product","A")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <f>GETPIVOTDATA("Metric",Count!A1,"Region","South","Product","B")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="e">
+        <f>GETPIVOTDATA("Metric",Count!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19">
+        <f>GETPIVOTDATA("Metric",CountNumbers!A1)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","North")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21">
+        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","South")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Product","A")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Product","B")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","North","Product","A")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26">
+        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","South","Product","B")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="e">
+        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28">
+        <f>GETPIVOTDATA("Metric",Average!A1)</f>
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29">
+        <f>GETPIVOTDATA("Metric",Average!A1,"Region","North")</f>
+        <v>9.3333333333333339</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30">
+        <f>GETPIVOTDATA("Metric",Average!A1,"Region","South")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31">
+        <f>GETPIVOTDATA("Metric",Average!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32">
+        <f>GETPIVOTDATA("Metric",Average!A1,"Product","A")</f>
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33">
+        <f>GETPIVOTDATA("Metric",Average!A1,"Product","B")</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34">
+        <f>GETPIVOTDATA("Metric",Average!A1,"Region","North","Product","A")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35">
+        <f>GETPIVOTDATA("Metric",Average!A1,"Region","South","Product","B")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="e">
+        <f>GETPIVOTDATA("Metric",Average!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37">
+        <f>GETPIVOTDATA("Metric",Minimum!A1)</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38">
+        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","North")</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39">
+        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","South")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40">
+        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41">
+        <f>GETPIVOTDATA("Metric",Minimum!A1,"Product","A")</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42">
+        <f>GETPIVOTDATA("Metric",Minimum!A1,"Product","B")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43">
+        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","North","Product","A")</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44">
+        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","South","Product","B")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" t="e">
+        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46">
+        <f>GETPIVOTDATA("Metric",Maximum!A1)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47">
+        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","North")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48">
+        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","South")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49">
+        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50">
+        <f>GETPIVOTDATA("Metric",Maximum!A1,"Product","A")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51">
+        <f>GETPIVOTDATA("Metric",Maximum!A1,"Product","B")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52">
+        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","North","Product","A")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53">
+        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","South","Product","B")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" t="e">
+        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55">
+        <f>GETPIVOTDATA("Metric",Product!A1)</f>
+        <v>-30000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>1</v>
+      </c>
+      <c r="B56">
+        <f>GETPIVOTDATA("Metric",Product!A1,"Region","North")</f>
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57">
+        <f>GETPIVOTDATA("Metric",Product!A1,"Region","South")</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58">
+        <f>GETPIVOTDATA("Metric",Product!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59">
+        <f>GETPIVOTDATA("Metric",Product!A1,"Product","A")</f>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>1</v>
+      </c>
+      <c r="B60">
+        <f>GETPIVOTDATA("Metric",Product!A1,"Product","B")</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>1</v>
+      </c>
+      <c r="B61">
+        <f>GETPIVOTDATA("Metric",Product!A1,"Region","North","Product","A")</f>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62">
+        <f>GETPIVOTDATA("Metric",Product!A1,"Region","South","Product","B")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B63" t="e">
+        <f>GETPIVOTDATA("Metric",Product!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64">
+        <f>GETPIVOTDATA("Metric",StandardDeviation!A1)</f>
+        <v>8.5615419172015965</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65">
+        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","North")</f>
+        <v>11.015141094572204</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66">
+        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","South")</f>
+        <v>7.0710678118654755</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67">
+        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68">
+        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Product","A")</f>
+        <v>6.0277137733417074</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69">
+        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Product","B")</f>
+        <v>3.5355339059327378</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70">
+        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","North","Product","A")</f>
+        <v>8.4852813742385695</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" t="e">
+        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","South","Product","B")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" t="e">
+        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>20</v>
+      </c>
+      <c r="B73">
+        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1)</f>
+        <v>7.657675887630659</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B74">
+        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","North")</f>
+        <v>8.9938250421546933</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>20</v>
+      </c>
+      <c r="B75">
+        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","South")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>20</v>
+      </c>
+      <c r="B76">
+        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>20</v>
+      </c>
+      <c r="B77">
+        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Product","A")</f>
+        <v>4.9216076867444665</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B78">
+        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Product","B")</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>20</v>
+      </c>
+      <c r="B79">
+        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","North","Product","A")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>20</v>
+      </c>
+      <c r="B80">
+        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","South","Product","B")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>20</v>
+      </c>
+      <c r="B81" t="e">
+        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82">
+        <f>GETPIVOTDATA("Metric",Variance!A1)</f>
+        <v>73.3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>21</v>
+      </c>
+      <c r="B83">
+        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","North")</f>
+        <v>121.33333333333334</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84">
+        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","South")</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>21</v>
+      </c>
+      <c r="B85">
+        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>21</v>
+      </c>
+      <c r="B86">
+        <f>GETPIVOTDATA("Metric",Variance!A1,"Product","A")</f>
+        <v>36.333333333333329</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>21</v>
+      </c>
+      <c r="B87">
+        <f>GETPIVOTDATA("Metric",Variance!A1,"Product","B")</f>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88">
+        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","North","Product","A")</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>21</v>
+      </c>
+      <c r="B89" t="e">
+        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","South","Product","B")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>21</v>
+      </c>
+      <c r="B90" t="e">
+        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91">
+        <f>GETPIVOTDATA("Metric",VarianceP!A1)</f>
+        <v>58.64</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92">
+        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","North")</f>
+        <v>80.888888888888886</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93">
+        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","South")</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94">
+        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","West")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95">
+        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Product","A")</f>
+        <v>24.222222222222221</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96">
+        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Product","B")</f>
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97">
+        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","North","Product","A")</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98">
+        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","South","Product","B")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" t="e">
+        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","missing")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>30</v>
+      </c>
+      <c r="B100" t="e">
+        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Error")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101">
+        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Literal")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>30</v>
+      </c>
+      <c r="B102">
+        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103">
+        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Single")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>30</v>
+      </c>
+      <c r="B104">
+        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>30</v>
+      </c>
+      <c r="B105">
+        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>31</v>
+      </c>
+      <c r="B106">
+        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Error")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>31</v>
+      </c>
+      <c r="B107">
+        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Literal")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>31</v>
+      </c>
+      <c r="B108">
+        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>31</v>
+      </c>
+      <c r="B109">
+        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Single")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>31</v>
+      </c>
+      <c r="B110">
+        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>31</v>
+      </c>
+      <c r="B111">
+        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>32</v>
+      </c>
+      <c r="B112">
+        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Error")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>32</v>
+      </c>
+      <c r="B113">
+        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Literal")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>32</v>
+      </c>
+      <c r="B114">
+        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>32</v>
+      </c>
+      <c r="B115">
+        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Single")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>32</v>
+      </c>
+      <c r="B116">
+        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>32</v>
+      </c>
+      <c r="B117">
+        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>33</v>
+      </c>
+      <c r="B118" t="e">
+        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Error")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" t="e">
+        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Literal")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>33</v>
+      </c>
+      <c r="B120">
+        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>33</v>
+      </c>
+      <c r="B121">
+        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Single")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>33</v>
+      </c>
+      <c r="B122" t="e">
+        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>33</v>
+      </c>
+      <c r="B123" t="e">
+        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>34</v>
+      </c>
+      <c r="B124" t="e">
+        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Error")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>34</v>
+      </c>
+      <c r="B125">
+        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Literal")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>34</v>
+      </c>
+      <c r="B126">
+        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>34</v>
+      </c>
+      <c r="B127">
+        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Single")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>34</v>
+      </c>
+      <c r="B128">
+        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>34</v>
+      </c>
+      <c r="B129">
+        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>35</v>
+      </c>
+      <c r="B130" t="e">
+        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Error")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>35</v>
+      </c>
+      <c r="B131">
+        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Literal")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>35</v>
+      </c>
+      <c r="B132">
+        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>35</v>
+      </c>
+      <c r="B133">
+        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Single")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>35</v>
+      </c>
+      <c r="B134">
+        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>35</v>
+      </c>
+      <c r="B135">
+        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>36</v>
+      </c>
+      <c r="B136" t="e">
+        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Error")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>36</v>
+      </c>
+      <c r="B137">
+        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Literal")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>36</v>
+      </c>
+      <c r="B138">
+        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>36</v>
+      </c>
+      <c r="B139">
+        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Single")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>36</v>
+      </c>
+      <c r="B140">
+        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>36</v>
+      </c>
+      <c r="B141">
+        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>37</v>
+      </c>
+      <c r="B142" t="e">
+        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Error")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>37</v>
+      </c>
+      <c r="B143" t="e">
+        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Literal")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>37</v>
+      </c>
+      <c r="B144">
+        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>37</v>
+      </c>
+      <c r="B145" t="e">
+        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Single")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>37</v>
+      </c>
+      <c r="B146" t="e">
+        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>37</v>
+      </c>
+      <c r="B147" t="e">
+        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>38</v>
+      </c>
+      <c r="B148" t="e">
+        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Error")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>38</v>
+      </c>
+      <c r="B149" t="e">
+        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Literal")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>38</v>
+      </c>
+      <c r="B150">
+        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>38</v>
+      </c>
+      <c r="B151">
+        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Single")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>38</v>
+      </c>
+      <c r="B152" t="e">
+        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>38</v>
+      </c>
+      <c r="B153" t="e">
+        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>39</v>
+      </c>
+      <c r="B154" t="e">
+        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Error")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>39</v>
+      </c>
+      <c r="B155" t="e">
+        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Literal")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>39</v>
+      </c>
+      <c r="B156">
+        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>39</v>
+      </c>
+      <c r="B157" t="e">
+        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Single")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>39</v>
+      </c>
+      <c r="B158" t="e">
+        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>39</v>
+      </c>
+      <c r="B159" t="e">
+        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>40</v>
+      </c>
+      <c r="B160" t="e">
+        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Error")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>40</v>
+      </c>
+      <c r="B161" t="e">
+        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Literal")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>40</v>
+      </c>
+      <c r="B162">
+        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Empty")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>40</v>
+      </c>
+      <c r="B163">
+        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Single")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>40</v>
+      </c>
+      <c r="B164" t="e">
+        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Boolean")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>40</v>
+      </c>
+      <c r="B165" t="e">
+        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","TextNumber")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9C61B02-5BDB-4B2E-B689-AACCB895950D}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>-2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3BFCC2D-93A0-4D78-91BC-E81BA4D80C56}">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2732,8 +4937,83 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB35CBA8-B00C-455F-BC70-F74F9C8037B9}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F73497-C812-4139-AD85-740CD7E260AE}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="str">
+        <f>"#N/A"</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="str">
+        <f>"12"</f>
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39E4FC5-3D8F-4C66-90F1-9F156D7F8302}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2768,13 +5048,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>9.3333333333333339</v>
+        <v>80.888888888888886</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -2782,13 +5062,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -2804,13 +5084,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>4.333333333333333</v>
+        <v>24.222222222222221</v>
       </c>
       <c r="C6" s="3">
-        <v>17.5</v>
+        <v>6.25</v>
       </c>
       <c r="D6" s="3">
-        <v>9.6</v>
+        <v>58.64</v>
       </c>
     </row>
   </sheetData>
@@ -2818,8 +5098,266 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A201A4-A715-45BB-9AB4-F08863B2D38C}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2EAD48D-4A6F-4B39-B60E-83C60FE4623D}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>72</v>
+      </c>
+      <c r="C3" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D3" s="3">
+        <v>121.33333333333334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C4" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D4" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>36.333333333333329</v>
+      </c>
+      <c r="C6" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>73.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A92727-DD3B-490C-9C6C-44E23A1A7EAE}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8.9938250421546933</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4.9216076867444665</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7.657675887630659</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDDF8AB1-9FE2-46CF-909D-C5222AAE4748}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>8.4852813742385695</v>
+      </c>
+      <c r="C3" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D3" s="3">
+        <v>11.015141094572204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C4" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7.0710678118654755</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6.0277137733417074</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3.5355339059327378</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8.5615419172015965</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2718F54-D9D0-470A-A622-1AC866A99400}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2855,13 +5393,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>2</v>
+        <v>-20</v>
       </c>
       <c r="C3" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3">
-        <v>3</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -2869,13 +5407,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3">
-        <v>2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -2891,13 +5429,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>-100</v>
       </c>
       <c r="C6" s="3">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="D6" s="3">
-        <v>5</v>
+        <v>-30000</v>
       </c>
     </row>
   </sheetData>
@@ -2905,8 +5443,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{381C0FAC-96ED-4C73-88D0-9865387979FF}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F48E771-E57D-4C48-9B8A-913F87123E4C}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2942,13 +5480,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -2956,13 +5494,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -2978,2314 +5516,6 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3">
-        <v>3</v>
-      </c>
-      <c r="D6" s="3">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF8E859-1CC4-4BF3-9D1A-2989317D2CE0}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>13</v>
-      </c>
-      <c r="C6" s="3">
-        <v>35</v>
-      </c>
-      <c r="D6" s="3">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5604004-D731-4F29-9267-9EA3C443DA9E}">
-  <dimension ref="A1:B165"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1">
-        <f>GETPIVOTDATA("Metric",Sum!A1)</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","North")</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","South")</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4">
-        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <f>GETPIVOTDATA("Metric",Sum!A1,"Product","A")</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6">
-        <f>GETPIVOTDATA("Metric",Sum!A1,"Product","B")</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","North","Product","A")</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","South","Product","B")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="e">
-        <f>GETPIVOTDATA("Metric",Sum!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <f>GETPIVOTDATA("Metric",Count!A1)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11">
-        <f>GETPIVOTDATA("Metric",Count!A1,"Region","North")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12">
-        <f>GETPIVOTDATA("Metric",Count!A1,"Region","South")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13">
-        <f>GETPIVOTDATA("Metric",Count!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <f>GETPIVOTDATA("Metric",Count!A1,"Product","A")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <f>GETPIVOTDATA("Metric",Count!A1,"Product","B")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <f>GETPIVOTDATA("Metric",Count!A1,"Region","North","Product","A")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17">
-        <f>GETPIVOTDATA("Metric",Count!A1,"Region","South","Product","B")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="e">
-        <f>GETPIVOTDATA("Metric",Count!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19">
-        <f>GETPIVOTDATA("Metric",CountNumbers!A1)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20">
-        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","North")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21">
-        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","South")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22">
-        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23">
-        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Product","A")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24">
-        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Product","B")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25">
-        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","North","Product","A")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26">
-        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","South","Product","B")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="e">
-        <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28">
-        <f>GETPIVOTDATA("Metric",Average!A1)</f>
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29">
-        <f>GETPIVOTDATA("Metric",Average!A1,"Region","North")</f>
-        <v>9.3333333333333339</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30">
-        <f>GETPIVOTDATA("Metric",Average!A1,"Region","South")</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31">
-        <f>GETPIVOTDATA("Metric",Average!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32">
-        <f>GETPIVOTDATA("Metric",Average!A1,"Product","A")</f>
-        <v>4.333333333333333</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>16</v>
-      </c>
-      <c r="B33">
-        <f>GETPIVOTDATA("Metric",Average!A1,"Product","B")</f>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34">
-        <f>GETPIVOTDATA("Metric",Average!A1,"Region","North","Product","A")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35">
-        <f>GETPIVOTDATA("Metric",Average!A1,"Region","South","Product","B")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B36" t="e">
-        <f>GETPIVOTDATA("Metric",Average!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37">
-        <f>GETPIVOTDATA("Metric",Minimum!A1)</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38">
-        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","North")</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39">
-        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","South")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40">
-        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41">
-        <f>GETPIVOTDATA("Metric",Minimum!A1,"Product","A")</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>17</v>
-      </c>
-      <c r="B42">
-        <f>GETPIVOTDATA("Metric",Minimum!A1,"Product","B")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43">
-        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","North","Product","A")</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44">
-        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","South","Product","B")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" t="e">
-        <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>18</v>
-      </c>
-      <c r="B46">
-        <f>GETPIVOTDATA("Metric",Maximum!A1)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47">
-        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","North")</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48">
-        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","South")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>18</v>
-      </c>
-      <c r="B49">
-        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>18</v>
-      </c>
-      <c r="B50">
-        <f>GETPIVOTDATA("Metric",Maximum!A1,"Product","A")</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>18</v>
-      </c>
-      <c r="B51">
-        <f>GETPIVOTDATA("Metric",Maximum!A1,"Product","B")</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>18</v>
-      </c>
-      <c r="B52">
-        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","North","Product","A")</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>18</v>
-      </c>
-      <c r="B53">
-        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","South","Product","B")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>18</v>
-      </c>
-      <c r="B54" t="e">
-        <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>1</v>
-      </c>
-      <c r="B55">
-        <f>GETPIVOTDATA("Metric",Product!A1)</f>
-        <v>-30000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>1</v>
-      </c>
-      <c r="B56">
-        <f>GETPIVOTDATA("Metric",Product!A1,"Region","North")</f>
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>1</v>
-      </c>
-      <c r="B57">
-        <f>GETPIVOTDATA("Metric",Product!A1,"Region","South")</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>1</v>
-      </c>
-      <c r="B58">
-        <f>GETPIVOTDATA("Metric",Product!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>1</v>
-      </c>
-      <c r="B59">
-        <f>GETPIVOTDATA("Metric",Product!A1,"Product","A")</f>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60">
-        <f>GETPIVOTDATA("Metric",Product!A1,"Product","B")</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>1</v>
-      </c>
-      <c r="B61">
-        <f>GETPIVOTDATA("Metric",Product!A1,"Region","North","Product","A")</f>
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>1</v>
-      </c>
-      <c r="B62">
-        <f>GETPIVOTDATA("Metric",Product!A1,"Region","South","Product","B")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>1</v>
-      </c>
-      <c r="B63" t="e">
-        <f>GETPIVOTDATA("Metric",Product!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>19</v>
-      </c>
-      <c r="B64">
-        <f>GETPIVOTDATA("Metric",StandardDeviation!A1)</f>
-        <v>8.5615419172015965</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>19</v>
-      </c>
-      <c r="B65">
-        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","North")</f>
-        <v>11.015141094572204</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>19</v>
-      </c>
-      <c r="B66">
-        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","South")</f>
-        <v>7.0710678118654755</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>19</v>
-      </c>
-      <c r="B67">
-        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>19</v>
-      </c>
-      <c r="B68">
-        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Product","A")</f>
-        <v>6.0277137733417074</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>19</v>
-      </c>
-      <c r="B69">
-        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Product","B")</f>
-        <v>3.5355339059327378</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>19</v>
-      </c>
-      <c r="B70">
-        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","North","Product","A")</f>
-        <v>8.4852813742385695</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>19</v>
-      </c>
-      <c r="B71" t="e">
-        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","South","Product","B")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>19</v>
-      </c>
-      <c r="B72" t="e">
-        <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>20</v>
-      </c>
-      <c r="B73">
-        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1)</f>
-        <v>7.657675887630659</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>20</v>
-      </c>
-      <c r="B74">
-        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","North")</f>
-        <v>8.9938250421546933</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>20</v>
-      </c>
-      <c r="B75">
-        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","South")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>20</v>
-      </c>
-      <c r="B76">
-        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>20</v>
-      </c>
-      <c r="B77">
-        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Product","A")</f>
-        <v>4.9216076867444665</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>20</v>
-      </c>
-      <c r="B78">
-        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Product","B")</f>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>20</v>
-      </c>
-      <c r="B79">
-        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","North","Product","A")</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>20</v>
-      </c>
-      <c r="B80">
-        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","South","Product","B")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>20</v>
-      </c>
-      <c r="B81" t="e">
-        <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>21</v>
-      </c>
-      <c r="B82">
-        <f>GETPIVOTDATA("Metric",Variance!A1)</f>
-        <v>73.3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>21</v>
-      </c>
-      <c r="B83">
-        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","North")</f>
-        <v>121.33333333333334</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>21</v>
-      </c>
-      <c r="B84">
-        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","South")</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>21</v>
-      </c>
-      <c r="B85">
-        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>21</v>
-      </c>
-      <c r="B86">
-        <f>GETPIVOTDATA("Metric",Variance!A1,"Product","A")</f>
-        <v>36.333333333333329</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>21</v>
-      </c>
-      <c r="B87">
-        <f>GETPIVOTDATA("Metric",Variance!A1,"Product","B")</f>
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88">
-        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","North","Product","A")</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>21</v>
-      </c>
-      <c r="B89" t="e">
-        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","South","Product","B")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>21</v>
-      </c>
-      <c r="B90" t="e">
-        <f>GETPIVOTDATA("Metric",Variance!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91">
-        <f>GETPIVOTDATA("Metric",VarianceP!A1)</f>
-        <v>58.64</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>22</v>
-      </c>
-      <c r="B92">
-        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","North")</f>
-        <v>80.888888888888886</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>22</v>
-      </c>
-      <c r="B93">
-        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","South")</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>22</v>
-      </c>
-      <c r="B94">
-        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","West")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>22</v>
-      </c>
-      <c r="B95">
-        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Product","A")</f>
-        <v>24.222222222222221</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>22</v>
-      </c>
-      <c r="B96">
-        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Product","B")</f>
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>22</v>
-      </c>
-      <c r="B97">
-        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","North","Product","A")</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98">
-        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","South","Product","B")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" t="e">
-        <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","missing")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>30</v>
-      </c>
-      <c r="B100" t="e">
-        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Error")</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>30</v>
-      </c>
-      <c r="B101">
-        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Literal")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>30</v>
-      </c>
-      <c r="B102">
-        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>30</v>
-      </c>
-      <c r="B103">
-        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Single")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>30</v>
-      </c>
-      <c r="B104">
-        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>30</v>
-      </c>
-      <c r="B105">
-        <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>31</v>
-      </c>
-      <c r="B106">
-        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Error")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>31</v>
-      </c>
-      <c r="B107">
-        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Literal")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>31</v>
-      </c>
-      <c r="B108">
-        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>31</v>
-      </c>
-      <c r="B109">
-        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Single")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>31</v>
-      </c>
-      <c r="B110">
-        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>31</v>
-      </c>
-      <c r="B111">
-        <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>32</v>
-      </c>
-      <c r="B112">
-        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Error")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>32</v>
-      </c>
-      <c r="B113">
-        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Literal")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>32</v>
-      </c>
-      <c r="B114">
-        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>32</v>
-      </c>
-      <c r="B115">
-        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Single")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>32</v>
-      </c>
-      <c r="B116">
-        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>32</v>
-      </c>
-      <c r="B117">
-        <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>33</v>
-      </c>
-      <c r="B118" t="e">
-        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Error")</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>33</v>
-      </c>
-      <c r="B119" t="e">
-        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Literal")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>33</v>
-      </c>
-      <c r="B120">
-        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>33</v>
-      </c>
-      <c r="B121">
-        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Single")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>33</v>
-      </c>
-      <c r="B122" t="e">
-        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>33</v>
-      </c>
-      <c r="B123" t="e">
-        <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>34</v>
-      </c>
-      <c r="B124" t="e">
-        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Error")</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>34</v>
-      </c>
-      <c r="B125">
-        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Literal")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>34</v>
-      </c>
-      <c r="B126">
-        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>34</v>
-      </c>
-      <c r="B127">
-        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Single")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>34</v>
-      </c>
-      <c r="B128">
-        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>34</v>
-      </c>
-      <c r="B129">
-        <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>35</v>
-      </c>
-      <c r="B130" t="e">
-        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Error")</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>35</v>
-      </c>
-      <c r="B131">
-        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Literal")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>35</v>
-      </c>
-      <c r="B132">
-        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>35</v>
-      </c>
-      <c r="B133">
-        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Single")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>35</v>
-      </c>
-      <c r="B134">
-        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>35</v>
-      </c>
-      <c r="B135">
-        <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>36</v>
-      </c>
-      <c r="B136" t="e">
-        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Error")</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>36</v>
-      </c>
-      <c r="B137">
-        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Literal")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>36</v>
-      </c>
-      <c r="B138">
-        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>36</v>
-      </c>
-      <c r="B139">
-        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Single")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>36</v>
-      </c>
-      <c r="B140">
-        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>36</v>
-      </c>
-      <c r="B141">
-        <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>37</v>
-      </c>
-      <c r="B142" t="e">
-        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Error")</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>37</v>
-      </c>
-      <c r="B143" t="e">
-        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Literal")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>37</v>
-      </c>
-      <c r="B144">
-        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>37</v>
-      </c>
-      <c r="B145" t="e">
-        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Single")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>37</v>
-      </c>
-      <c r="B146" t="e">
-        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>37</v>
-      </c>
-      <c r="B147" t="e">
-        <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>38</v>
-      </c>
-      <c r="B148" t="e">
-        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Error")</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>38</v>
-      </c>
-      <c r="B149" t="e">
-        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Literal")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>38</v>
-      </c>
-      <c r="B150">
-        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>38</v>
-      </c>
-      <c r="B151">
-        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Single")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>38</v>
-      </c>
-      <c r="B152" t="e">
-        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>38</v>
-      </c>
-      <c r="B153" t="e">
-        <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>39</v>
-      </c>
-      <c r="B154" t="e">
-        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Error")</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>39</v>
-      </c>
-      <c r="B155" t="e">
-        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Literal")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>39</v>
-      </c>
-      <c r="B156">
-        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>39</v>
-      </c>
-      <c r="B157" t="e">
-        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Single")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>39</v>
-      </c>
-      <c r="B158" t="e">
-        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>39</v>
-      </c>
-      <c r="B159" t="e">
-        <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>40</v>
-      </c>
-      <c r="B160" t="e">
-        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Error")</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>40</v>
-      </c>
-      <c r="B161" t="e">
-        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Literal")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>40</v>
-      </c>
-      <c r="B162">
-        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Empty")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>40</v>
-      </c>
-      <c r="B163">
-        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Single")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>40</v>
-      </c>
-      <c r="B164" t="e">
-        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Boolean")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>40</v>
-      </c>
-      <c r="B165" t="e">
-        <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","TextNumber")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AAE98F-72CC-4524-BD61-6D2C6C78ED09}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>20</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>-2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521F8A0E-5FBA-418D-A0B8-F11B3A5B9901}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="e">
-        <f>NA()</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="str">
-        <f>"#N/A"</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" t="str">
-        <f>"12"</f>
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F45ADBC-3C69-4F3C-AAAB-B8C640933A7B}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>36</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>80.888888888888886</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>24.222222222222221</v>
-      </c>
-      <c r="C6" s="3">
-        <v>6.25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>58.64</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D880C88-EF05-43E4-A70D-6D8C4EE31608}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>72</v>
-      </c>
-      <c r="C3" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D3" s="3">
-        <v>121.33333333333334</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C4" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D4" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>36.333333333333329</v>
-      </c>
-      <c r="C6" s="3">
-        <v>12.5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>73.3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C2BF7C-EB7E-4C4F-AC4B-5DF9679CC1A3}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>8.9938250421546933</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>4.9216076867444665</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>7.657675887630659</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E334FB7E-517A-4DE3-92F6-D29DF1779CB8}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>8.4852813742385695</v>
-      </c>
-      <c r="C3" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D3" s="3">
-        <v>11.015141094572204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C4" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D4" s="3">
-        <v>7.0710678118654755</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>6.0277137733417074</v>
-      </c>
-      <c r="C6" s="3">
-        <v>3.5355339059327378</v>
-      </c>
-      <c r="D6" s="3">
-        <v>8.5615419172015965</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA88652-4A67-4FFF-A9F7-4E046658B2B5}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>-20</v>
-      </c>
-      <c r="C3" s="3">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>-100</v>
-      </c>
-      <c r="C6" s="3">
-        <v>300</v>
-      </c>
-      <c r="D6" s="3">
-        <v>-30000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74DC1507-5EE3-40C8-9BC8-FF5EE9058D21}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
         <v>10</v>
       </c>
       <c r="C6" s="3">
@@ -5293,93 +5523,6 @@
       </c>
       <c r="D6" s="3">
         <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED469F01-3792-4A85-A7B4-6342AEB56B90}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>-2</v>
-      </c>
-      <c r="C3" s="3">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>-2</v>
-      </c>
-      <c r="C6" s="3">
-        <v>15</v>
-      </c>
-      <c r="D6" s="3">
-        <v>-2</v>
       </c>
     </row>
   </sheetData>

--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/aggregation-conformance.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/aggregation-conformance.xlsx
@@ -8,42 +8,55 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B882E7FC-DB9E-4B3F-8E0B-DB3347118C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{029A2B9A-DE23-4A58-84FC-0EA9E2AEE02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{3E1EE5EB-53F1-408B-A92B-0651D5ADE064}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B6A831D1-D89B-4ABF-892C-2FD4021EB0A5}"/>
   </bookViews>
   <sheets>
-    <sheet name="LookupEdges" sheetId="16" r:id="rId1"/>
-    <sheet name="ErrorGroups" sheetId="15" r:id="rId2"/>
-    <sheet name="ErrorSource" sheetId="14" r:id="rId3"/>
-    <sheet name="VarianceP" sheetId="13" r:id="rId4"/>
-    <sheet name="Variance" sheetId="12" r:id="rId5"/>
-    <sheet name="StandardDeviationP" sheetId="11" r:id="rId6"/>
-    <sheet name="StandardDeviation" sheetId="10" r:id="rId7"/>
-    <sheet name="Product" sheetId="9" r:id="rId8"/>
-    <sheet name="Maximum" sheetId="8" r:id="rId9"/>
-    <sheet name="Minimum" sheetId="7" r:id="rId10"/>
-    <sheet name="Average" sheetId="6" r:id="rId11"/>
-    <sheet name="CountNumbers" sheetId="5" r:id="rId12"/>
-    <sheet name="Count" sheetId="4" r:id="rId13"/>
-    <sheet name="Sum" sheetId="3" r:id="rId14"/>
-    <sheet name="Lookups" sheetId="2" r:id="rId15"/>
-    <sheet name="Source" sheetId="1" r:id="rId16"/>
+    <sheet name="LookupEdges" sheetId="23" r:id="rId1"/>
+    <sheet name="ErrorNumbers" sheetId="22" r:id="rId2"/>
+    <sheet name="ErrorCount" sheetId="21" r:id="rId3"/>
+    <sheet name="Keys" sheetId="20" r:id="rId4"/>
+    <sheet name="KeySource" sheetId="19" r:id="rId5"/>
+    <sheet name="Scalar" sheetId="18" r:id="rId6"/>
+    <sheet name="ColumnsOnly" sheetId="17" r:id="rId7"/>
+    <sheet name="RowsOnly" sheetId="16" r:id="rId8"/>
+    <sheet name="ErrorGroups" sheetId="15" r:id="rId9"/>
+    <sheet name="ErrorSource" sheetId="14" r:id="rId10"/>
+    <sheet name="VarianceP" sheetId="13" r:id="rId11"/>
+    <sheet name="Variance" sheetId="12" r:id="rId12"/>
+    <sheet name="StandardDeviationP" sheetId="11" r:id="rId13"/>
+    <sheet name="StandardDeviation" sheetId="10" r:id="rId14"/>
+    <sheet name="Product" sheetId="9" r:id="rId15"/>
+    <sheet name="Maximum" sheetId="8" r:id="rId16"/>
+    <sheet name="Minimum" sheetId="7" r:id="rId17"/>
+    <sheet name="Average" sheetId="6" r:id="rId18"/>
+    <sheet name="CountNumbers" sheetId="5" r:id="rId19"/>
+    <sheet name="Count" sheetId="4" r:id="rId20"/>
+    <sheet name="Sum" sheetId="3" r:id="rId21"/>
+    <sheet name="Lookups" sheetId="2" r:id="rId22"/>
+    <sheet name="Source" sheetId="1" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId17"/>
-    <pivotCache cacheId="19" r:id="rId18"/>
-    <pivotCache cacheId="29" r:id="rId19"/>
-    <pivotCache cacheId="39" r:id="rId20"/>
-    <pivotCache cacheId="49" r:id="rId21"/>
-    <pivotCache cacheId="59" r:id="rId22"/>
-    <pivotCache cacheId="69" r:id="rId23"/>
-    <pivotCache cacheId="79" r:id="rId24"/>
-    <pivotCache cacheId="89" r:id="rId25"/>
-    <pivotCache cacheId="99" r:id="rId26"/>
-    <pivotCache cacheId="109" r:id="rId27"/>
-    <pivotCache cacheId="117" r:id="rId28"/>
+    <pivotCache cacheId="9" r:id="rId24"/>
+    <pivotCache cacheId="19" r:id="rId25"/>
+    <pivotCache cacheId="29" r:id="rId26"/>
+    <pivotCache cacheId="39" r:id="rId27"/>
+    <pivotCache cacheId="49" r:id="rId28"/>
+    <pivotCache cacheId="59" r:id="rId29"/>
+    <pivotCache cacheId="69" r:id="rId30"/>
+    <pivotCache cacheId="79" r:id="rId31"/>
+    <pivotCache cacheId="89" r:id="rId32"/>
+    <pivotCache cacheId="99" r:id="rId33"/>
+    <pivotCache cacheId="109" r:id="rId34"/>
+    <pivotCache cacheId="117" r:id="rId35"/>
+    <pivotCache cacheId="125" r:id="rId36"/>
+    <pivotCache cacheId="133" r:id="rId37"/>
+    <pivotCache cacheId="139" r:id="rId38"/>
+    <pivotCache cacheId="147" r:id="rId39"/>
+    <pivotCache cacheId="155" r:id="rId40"/>
+    <pivotCache cacheId="163" r:id="rId41"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -68,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="48">
   <si>
     <t>Region</t>
   </si>
@@ -104,6 +117,9 @@
   </si>
   <si>
     <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
   </si>
   <si>
     <t>Metric</t>
@@ -192,6 +208,24 @@
   <si>
     <t>Error VarianceP</t>
   </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> North </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> north </t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
 </sst>
 </file>
 
@@ -227,13 +261,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -252,7 +287,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658789814814" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{213C3A12-7F95-4031-AB2F-0DFD676DA18A}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692584606484" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{BB3F26A6-0289-4759-BBC3-4DAFD2AC601B}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -286,7 +321,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.65879710648" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{23A19AC0-19E5-48C4-A05D-8334BDD0D15F}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692596875" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{2FFA7601-6FCB-45D9-814E-53207CEDD293}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -320,7 +355,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658797916665" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{9AE02201-051C-458C-AB4D-1C4C5074300A}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692598148147" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{4AE34E63-1A6F-497A-B635-3D17588254E8}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -354,7 +389,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658802662037" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{AC9CCD48-357C-4DDD-85DB-5F3D34C5C6E2}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692606481483" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{F45278CC-6785-483A-9E33-1436F8631C1A}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="ErrorSource"/>
   </cacheSource>
@@ -381,8 +416,181 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692606944445" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{2A7E38E6-EA58-475C-8E7A-DA36DCC0A6B0}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D9" sheet="Source"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="3">
+        <s v="North"/>
+        <s v="South"/>
+        <s v="West"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="-2" maxValue="20"/>
+    </cacheField>
+    <cacheField name="Units" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692607175923" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{75BFE042-F91A-4E00-BAA7-1BF46D9F8D10}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D9" sheet="Source"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="2">
+        <s v="A"/>
+        <s v="B"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="-2" maxValue="20"/>
+    </cacheField>
+    <cacheField name="Units" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692607407407" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{EF63A92D-D35C-4B83-BB09-5EEFC88588F1}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D9" sheet="Source"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="-2" maxValue="20"/>
+    </cacheField>
+    <cacheField name="Units" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692608796293" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{D64ECEEF-1079-456A-B654-401DD1B79D45}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:B9" sheet="KeySource"/>
+  </cacheSource>
+  <cacheFields count="2">
+    <cacheField name="Key" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1" count="7">
+        <n v="1"/>
+        <s v="1"/>
+        <b v="1"/>
+        <s v="TRUE"/>
+        <s v=" North "/>
+        <s v="North"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="19"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692609259262" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{325431CE-462C-4F8B-8EE4-098C7CCA4EA7}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:B8" sheet="ErrorSource"/>
+  </cacheSource>
+  <cacheFields count="2">
+    <cacheField name="Group" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Error"/>
+        <s v="Literal"/>
+        <s v="Empty"/>
+        <s v="Single"/>
+        <s v="Boolean"/>
+        <s v="TextNumber"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="5"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692609606478" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{A25B856F-11A5-472B-A076-6B937ED34B35}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:B8" sheet="ErrorSource"/>
+  </cacheSource>
+  <cacheFields count="2">
+    <cacheField name="Group" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Error"/>
+        <s v="Literal"/>
+        <s v="Empty"/>
+        <s v="Single"/>
+        <s v="Boolean"/>
+        <s v="TextNumber"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="5"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658790856483" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{2BC03678-FBB0-47E9-ADC6-5CC3791277A4}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692586226854" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{944243EC-7987-426C-BFB7-7E0C2E6033AC}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -416,7 +624,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658791550923" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{6FF4B22B-F1AF-45E2-AAE1-6C24335E59C7}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692587500002" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{860DA2AA-6DC9-4D7E-B0D4-8C3E71204D11}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -450,7 +658,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658792245369" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{E60A7CEF-2149-4B98-82EF-EF457C42E97A}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.69258865741" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{1E45C317-9859-4255-8162-BF5D5513D43E}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -484,7 +692,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658792939816" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{7A645670-8CF9-4605-8669-6A848EF6173A}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692590162034" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{1277745F-D840-4720-ACEE-55DC4C7FE492}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -518,7 +726,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658793750001" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{9052A462-4DC9-4DFA-AF7A-C92F86F25761}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692591435189" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{DFCD5C00-87B3-459C-AA7F-4B4951A86E82}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -552,7 +760,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658794675925" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{49F60F01-5BED-4AAE-BA95-36CC68C82EE6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692592824074" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{3CF9C00A-29EA-4B33-B2E8-952847B56571}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -586,7 +794,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.65879548611" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{274F422E-813F-411A-B03C-F9EC99F1C609}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692594097221" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{BA444D6D-A003-478F-9DB5-255E63FEE4BD}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -620,7 +828,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.658796296295" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{4BA254D4-7DA4-441F-9D62-2CDB6281980A}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46292.692595370369" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{56A45341-3A55-49EB-BB7E-207441E51E58}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D9" sheet="Source"/>
   </cacheSource>
@@ -845,6 +1053,268 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="8">
+  <r>
+    <x v="0"/>
+    <s v="A"/>
+    <n v="10"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="A"/>
+    <n v="5"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="B"/>
+    <n v="15"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="A"/>
+    <n v="-2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="B"/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="A"/>
+    <s v="pending"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="B"/>
+    <b v="1"/>
+    <n v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="8">
+  <r>
+    <s v="North"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="North"/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="South"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="South"/>
+    <x v="1"/>
+    <n v="15"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <s v="North"/>
+    <x v="0"/>
+    <n v="-2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="West"/>
+    <x v="1"/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <s v="South"/>
+    <x v="0"/>
+    <s v="pending"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="North"/>
+    <x v="1"/>
+    <b v="1"/>
+    <n v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="8">
+  <r>
+    <s v="North"/>
+    <s v="A"/>
+    <n v="10"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="North"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="South"/>
+    <s v="A"/>
+    <n v="5"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="South"/>
+    <s v="B"/>
+    <n v="15"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <s v="North"/>
+    <s v="A"/>
+    <n v="-2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="West"/>
+    <s v="B"/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <s v="South"/>
+    <s v="A"/>
+    <s v="pending"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="North"/>
+    <s v="B"/>
+    <b v="1"/>
+    <n v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="8">
+  <r>
+    <x v="0"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="13"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="17"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="19"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="7">
+  <r>
+    <x v="0"/>
+    <e v="#N/A"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="#N/A"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <b v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="12"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="7">
+  <r>
+    <x v="0"/>
+    <e v="#N/A"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="#N/A"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <b v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="12"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="8">
   <r>
@@ -1270,7 +1740,935 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37E92055-9170-482B-93D5-D9DE7ECBA4A6}" name="PivotErrorGroups" cacheId="117" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31DE75AD-CBD0-46C7-B208-11909C4C4F7C}" name="PivotErrorNumbers" cacheId="163" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="1" subtotal="countNums" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{113A3D2B-DD09-48E9-8CCF-F1A739726122}" name="PivotStandardDeviationP" cacheId="89" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" subtotal="stdDevp" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AE51B36C-A19D-45B0-A46E-73F308AFDBB2}" name="PivotStandardDeviation" cacheId="79" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" subtotal="stdDev" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA9D4374-0F02-4F58-A759-3624E8DB4B7B}" name="PivotProduct" cacheId="69" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" subtotal="product" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4CFD9FD8-5219-4360-82FA-796607D06430}" name="PivotMaximum" cacheId="59" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" subtotal="max" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3115B16D-4FD0-4DA6-A2CA-CEAFA35CB6D7}" name="PivotMinimum" cacheId="49" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" subtotal="min" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A605D7C-0AD5-44D0-B26D-593EB8C8C63B}" name="PivotAverage" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C3F3D69-0284-4CB2-B657-838BEE00E23E}" name="PivotCountNumbers" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" subtotal="countNums" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1F9275AB-FF84-4D09-BEE1-CA8E011FD791}" name="PivotCount" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1909B9DE-EC6A-4F0B-AFC7-188FD4719EAA}" name="PivotSum" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09E49A46-7BC5-4811-BE5D-A5A7203333F5}" name="PivotErrorCount" cacheId="155" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE62957D-0947-4311-8D1C-783162C5FABD}" name="PivotKeys" cacheId="147" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{015499C7-58CC-4D8E-B412-B031C99BCC2C}" name="PivotScalar" cacheId="139" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:A2" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D39A8BCB-29A0-4139-9C23-D2CC98AF08AB}" name="PivotColumnsOnly" cacheId="133" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:D3" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D6D2C4D5-53E1-46B2-92CE-CB426E89C664}" name="PivotRowsOnly" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sumSubtotal="1" countASubtotal="1" avgSubtotal="1" maxSubtotal="1" minSubtotal="1" productSubtotal="1" countSubtotal="1" stdDevSubtotal="1" stdDevPSubtotal="1" varSubtotal="1" varPSubtotal="1">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="sum"/>
+        <item t="countA"/>
+        <item t="avg"/>
+        <item t="max"/>
+        <item t="min"/>
+        <item t="product"/>
+        <item t="count"/>
+        <item t="stdDev"/>
+        <item t="stdDevP"/>
+        <item t="var"/>
+        <item t="varP"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Metric" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64AEAE54-B037-4CFD-B355-0373EA47D7AF}" name="PivotErrorGroups" cacheId="117" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:L8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
@@ -1375,8 +2773,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6058C8B8-9986-4DF3-AAD6-DCEC37425A1E}" name="PivotCountNumbers" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{047601E8-2A8C-4F27-A5F2-3F9A0E78216C}" name="PivotVarianceP" cacheId="109" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1428,7 +2826,7 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Metric" fld="2" subtotal="countNums" baseField="0" baseItem="0"/>
+    <dataField name="Metric" fld="2" subtotal="varp" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -1442,8 +2840,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39850292-163F-47AE-9C58-9C5046602472}" name="PivotCount" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E8A50F5-D1A2-484D-B705-B1F832FC7759}" name="PivotVariance" cacheId="99" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -1495,610 +2893,7 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Metric" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{97D9914D-9FF5-431C-B8BC-9831E2DA7E3F}" name="PivotSum" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Metric" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3BA77F5B-15AA-489B-88A1-5CD68AE0A747}" name="PivotVarianceP" cacheId="109" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Metric" fld="2" subtotal="varp" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D1D96C1-37EB-4E05-BCBD-0BC067E9701D}" name="PivotVariance" cacheId="99" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
     <dataField name="Metric" fld="2" subtotal="var" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04319975-3807-4EA2-9C67-344EA160698E}" name="PivotStandardDeviationP" cacheId="89" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Metric" fld="2" subtotal="stdDevp" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FAFD2AF-BF41-4D45-9FE0-68E750742265}" name="PivotStandardDeviation" cacheId="79" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Metric" fld="2" subtotal="stdDev" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3FCF7C71-FD19-4E1B-922A-BC0071CDDE02}" name="PivotProduct" cacheId="69" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Metric" fld="2" subtotal="product" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C227D33-B72B-4E23-AD49-B0EA618FCFB1}" name="PivotMaximum" cacheId="59" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Metric" fld="2" subtotal="max" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2AB65852-B67F-4B84-ACCF-8BE183442F56}" name="PivotMinimum" cacheId="49" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Metric" fld="2" subtotal="min" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DD63A28E-3CFC-4E82-9D1C-513961A59241}" name="PivotAverage" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Metric" fld="2" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -2428,8 +3223,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6ABF11-90F5-4A64-85C3-47D415AD811C}">
-  <dimension ref="A1:A22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0AFAC3-54DA-47C0-B64C-07AE193A9D80}">
+  <dimension ref="A1:A35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -2564,13 +3359,510 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <f>GETPIVOTDATA("Metric",RowsOnly!A1,"Region","North")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <f>GETPIVOTDATA("Metric",ColumnsOnly!A1,"Product","B")</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <f>GETPIVOTDATA("Metric",Scalar!A1)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <f>GETPIVOTDATA("Metric",Keys!A1,"Key",1)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <f>GETPIVOTDATA("Metric",Keys!A1,"Key","1")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <f>GETPIVOTDATA("Metric",Keys!A1,"Key",TRUE())</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <f>GETPIVOTDATA("Metric",Keys!A1,"Key","TRUE")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <f>GETPIVOTDATA("Metric",Keys!A1,"Key"," North ")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <f>GETPIVOTDATA("Metric",Keys!A1,"Key","North")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <f>GETPIVOTDATA("Metric",Keys!A1,"Key"," north ")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <f>GETPIVOTDATA("Metric",Keys!A1,"Key","(blank)")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <f>GETPIVOTDATA("Metric",ErrorCount!A1)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <f>GETPIVOTDATA("Metric",ErrorNumbers!A1)</f>
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D103399-47F3-47D2-9A1D-016145D8F614}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E911F2-3629-43EB-9DF4-2F97C21CC3F2}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="str">
+        <f>"#N/A"</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="str">
+        <f>"12"</f>
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3DC45E-938A-4F00-AB7F-101D0D251A70}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>36</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>80.888888888888886</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>24.222222222222221</v>
+      </c>
+      <c r="C6" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>58.64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{833D04B6-1E43-4C99-94EF-3114B23F1AA0}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>72</v>
+      </c>
+      <c r="C3" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D3" s="3">
+        <v>121.33333333333334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C4" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D4" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>36.333333333333329</v>
+      </c>
+      <c r="C6" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>73.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C19A8F-6E61-4C6F-8B89-B03BA1EFDBAC}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8.9938250421546933</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4.9216076867444665</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7.657675887630659</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EB0B5C8-842B-41AA-9ACD-E7D5166DDE04}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>8.4852813742385695</v>
+      </c>
+      <c r="C3" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D3" s="3">
+        <v>11.015141094572204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C4" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7.0710678118654755</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6.0277137733417074</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3.5355339059327378</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8.5615419172015965</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FB9961-9965-4A30-B27E-974E3794B0EA}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2581,7 +3873,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2606,13 +3898,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>-2</v>
+        <v>-20</v>
       </c>
       <c r="C3" s="3">
         <v>20</v>
       </c>
       <c r="D3" s="3">
-        <v>-2</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -2626,7 +3918,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="3">
-        <v>5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -2642,13 +3934,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>-2</v>
+        <v>-100</v>
       </c>
       <c r="C6" s="3">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="D6" s="3">
-        <v>-2</v>
+        <v>-30000</v>
       </c>
     </row>
   </sheetData>
@@ -2656,94 +3948,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8914D4A-8D2B-45F9-BA2F-15240B271009}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3">
-        <v>9.3333333333333339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>4.333333333333333</v>
-      </c>
-      <c r="C6" s="3">
-        <v>17.5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>9.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ECD3F9C-B9DF-4218-AA76-DE9F06117257}">
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E045F78-998F-4418-AC97-AD7126E589CF}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2754,7 +3960,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2779,13 +3985,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -2793,13 +3999,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -2815,13 +4021,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2829,8 +4035,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DBDC9F4-3908-4676-9356-9D0C9B26F64E}">
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E75DE85-1F44-42A0-80B1-1E268E44FC7A}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2841,7 +4047,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2866,13 +4072,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="C3" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -2880,13 +4086,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -2902,13 +4108,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="C6" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3">
-        <v>7</v>
+        <v>-2</v>
       </c>
     </row>
   </sheetData>
@@ -2916,8 +4122,94 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155D7EB4-54D0-46F8-BB19-439B4F7B4755}">
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0262A13F-C744-4E76-98C4-E7D937572986}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3">
+        <v>9.3333333333333339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="C6" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>9.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E506BD9C-E4EB-4C7F-983D-850D7EBB667A}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2928,7 +4220,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2953,13 +4245,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -2967,13 +4259,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -2989,13 +4281,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3003,14 +4295,264 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49DA6248-ED1D-40D3-B4CB-4907CCE5B963}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFEF5DFB-CCB6-4469-9367-D6D0034F4C50}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE9A2D7-F0C8-4682-8189-F5F89DF40998}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2A5771D-BFCC-4F77-A705-2F9B185434C6}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3">
+        <v>35</v>
+      </c>
+      <c r="D6" s="3">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12460FF-3754-4BA5-915B-5DD8018BBC18}">
   <dimension ref="A1:B165"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1">
         <f>GETPIVOTDATA("Metric",Sum!A1)</f>
@@ -3019,7 +4561,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <f>GETPIVOTDATA("Metric",Sum!A1,"Region","North")</f>
@@ -3028,7 +4570,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <f>GETPIVOTDATA("Metric",Sum!A1,"Region","South")</f>
@@ -3037,7 +4579,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <f>GETPIVOTDATA("Metric",Sum!A1,"Region","West")</f>
@@ -3046,7 +4588,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <f>GETPIVOTDATA("Metric",Sum!A1,"Product","A")</f>
@@ -3055,7 +4597,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <f>GETPIVOTDATA("Metric",Sum!A1,"Product","B")</f>
@@ -3064,7 +4606,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <f>GETPIVOTDATA("Metric",Sum!A1,"Region","North","Product","A")</f>
@@ -3073,7 +4615,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <f>GETPIVOTDATA("Metric",Sum!A1,"Region","South","Product","B")</f>
@@ -3082,7 +4624,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="e">
         <f>GETPIVOTDATA("Metric",Sum!A1,"Region","missing")</f>
@@ -3091,7 +4633,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <f>GETPIVOTDATA("Metric",Count!A1)</f>
@@ -3100,7 +4642,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <f>GETPIVOTDATA("Metric",Count!A1,"Region","North")</f>
@@ -3109,7 +4651,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <f>GETPIVOTDATA("Metric",Count!A1,"Region","South")</f>
@@ -3118,7 +4660,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <f>GETPIVOTDATA("Metric",Count!A1,"Region","West")</f>
@@ -3127,7 +4669,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <f>GETPIVOTDATA("Metric",Count!A1,"Product","A")</f>
@@ -3136,7 +4678,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <f>GETPIVOTDATA("Metric",Count!A1,"Product","B")</f>
@@ -3145,7 +4687,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <f>GETPIVOTDATA("Metric",Count!A1,"Region","North","Product","A")</f>
@@ -3154,7 +4696,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <f>GETPIVOTDATA("Metric",Count!A1,"Region","South","Product","B")</f>
@@ -3163,7 +4705,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="e">
         <f>GETPIVOTDATA("Metric",Count!A1,"Region","missing")</f>
@@ -3172,7 +4714,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <f>GETPIVOTDATA("Metric",CountNumbers!A1)</f>
@@ -3181,7 +4723,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","North")</f>
@@ -3190,7 +4732,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","South")</f>
@@ -3199,7 +4741,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22">
         <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","West")</f>
@@ -3208,7 +4750,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23">
         <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Product","A")</f>
@@ -3217,7 +4759,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24">
         <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Product","B")</f>
@@ -3226,7 +4768,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25">
         <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","North","Product","A")</f>
@@ -3235,7 +4777,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B26">
         <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","South","Product","B")</f>
@@ -3244,7 +4786,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" t="e">
         <f>GETPIVOTDATA("Metric",CountNumbers!A1,"Region","missing")</f>
@@ -3253,7 +4795,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B28">
         <f>GETPIVOTDATA("Metric",Average!A1)</f>
@@ -3262,7 +4804,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B29">
         <f>GETPIVOTDATA("Metric",Average!A1,"Region","North")</f>
@@ -3271,7 +4813,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B30">
         <f>GETPIVOTDATA("Metric",Average!A1,"Region","South")</f>
@@ -3280,7 +4822,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B31">
         <f>GETPIVOTDATA("Metric",Average!A1,"Region","West")</f>
@@ -3289,7 +4831,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B32">
         <f>GETPIVOTDATA("Metric",Average!A1,"Product","A")</f>
@@ -3298,7 +4840,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B33">
         <f>GETPIVOTDATA("Metric",Average!A1,"Product","B")</f>
@@ -3307,7 +4849,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B34">
         <f>GETPIVOTDATA("Metric",Average!A1,"Region","North","Product","A")</f>
@@ -3316,7 +4858,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B35">
         <f>GETPIVOTDATA("Metric",Average!A1,"Region","South","Product","B")</f>
@@ -3325,7 +4867,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B36" t="e">
         <f>GETPIVOTDATA("Metric",Average!A1,"Region","missing")</f>
@@ -3334,7 +4876,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B37">
         <f>GETPIVOTDATA("Metric",Minimum!A1)</f>
@@ -3343,7 +4885,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B38">
         <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","North")</f>
@@ -3352,7 +4894,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B39">
         <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","South")</f>
@@ -3361,7 +4903,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B40">
         <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","West")</f>
@@ -3370,7 +4912,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B41">
         <f>GETPIVOTDATA("Metric",Minimum!A1,"Product","A")</f>
@@ -3379,7 +4921,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B42">
         <f>GETPIVOTDATA("Metric",Minimum!A1,"Product","B")</f>
@@ -3388,7 +4930,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B43">
         <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","North","Product","A")</f>
@@ -3397,7 +4939,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44">
         <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","South","Product","B")</f>
@@ -3406,7 +4948,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B45" t="e">
         <f>GETPIVOTDATA("Metric",Minimum!A1,"Region","missing")</f>
@@ -3415,7 +4957,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B46">
         <f>GETPIVOTDATA("Metric",Maximum!A1)</f>
@@ -3424,7 +4966,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B47">
         <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","North")</f>
@@ -3433,7 +4975,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B48">
         <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","South")</f>
@@ -3442,7 +4984,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B49">
         <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","West")</f>
@@ -3451,7 +4993,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B50">
         <f>GETPIVOTDATA("Metric",Maximum!A1,"Product","A")</f>
@@ -3460,7 +5002,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B51">
         <f>GETPIVOTDATA("Metric",Maximum!A1,"Product","B")</f>
@@ -3469,7 +5011,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B52">
         <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","North","Product","A")</f>
@@ -3478,7 +5020,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B53">
         <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","South","Product","B")</f>
@@ -3487,7 +5029,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B54" t="e">
         <f>GETPIVOTDATA("Metric",Maximum!A1,"Region","missing")</f>
@@ -3577,7 +5119,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B64">
         <f>GETPIVOTDATA("Metric",StandardDeviation!A1)</f>
@@ -3586,7 +5128,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B65">
         <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","North")</f>
@@ -3595,7 +5137,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B66">
         <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","South")</f>
@@ -3604,7 +5146,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B67">
         <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","West")</f>
@@ -3613,7 +5155,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B68">
         <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Product","A")</f>
@@ -3622,7 +5164,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B69">
         <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Product","B")</f>
@@ -3631,7 +5173,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B70">
         <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","North","Product","A")</f>
@@ -3640,7 +5182,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B71" t="e">
         <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","South","Product","B")</f>
@@ -3649,7 +5191,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B72" t="e">
         <f>GETPIVOTDATA("Metric",StandardDeviation!A1,"Region","missing")</f>
@@ -3658,7 +5200,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B73">
         <f>GETPIVOTDATA("Metric",StandardDeviationP!A1)</f>
@@ -3667,7 +5209,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B74">
         <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","North")</f>
@@ -3676,7 +5218,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B75">
         <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","South")</f>
@@ -3685,7 +5227,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B76">
         <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","West")</f>
@@ -3694,7 +5236,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B77">
         <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Product","A")</f>
@@ -3703,7 +5245,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B78">
         <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Product","B")</f>
@@ -3712,7 +5254,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B79">
         <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","North","Product","A")</f>
@@ -3721,7 +5263,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B80">
         <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","South","Product","B")</f>
@@ -3730,7 +5272,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B81" t="e">
         <f>GETPIVOTDATA("Metric",StandardDeviationP!A1,"Region","missing")</f>
@@ -3739,7 +5281,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B82">
         <f>GETPIVOTDATA("Metric",Variance!A1)</f>
@@ -3748,7 +5290,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B83">
         <f>GETPIVOTDATA("Metric",Variance!A1,"Region","North")</f>
@@ -3757,7 +5299,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B84">
         <f>GETPIVOTDATA("Metric",Variance!A1,"Region","South")</f>
@@ -3766,7 +5308,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B85">
         <f>GETPIVOTDATA("Metric",Variance!A1,"Region","West")</f>
@@ -3775,7 +5317,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B86">
         <f>GETPIVOTDATA("Metric",Variance!A1,"Product","A")</f>
@@ -3784,7 +5326,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B87">
         <f>GETPIVOTDATA("Metric",Variance!A1,"Product","B")</f>
@@ -3793,7 +5335,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B88">
         <f>GETPIVOTDATA("Metric",Variance!A1,"Region","North","Product","A")</f>
@@ -3802,7 +5344,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B89" t="e">
         <f>GETPIVOTDATA("Metric",Variance!A1,"Region","South","Product","B")</f>
@@ -3811,7 +5353,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B90" t="e">
         <f>GETPIVOTDATA("Metric",Variance!A1,"Region","missing")</f>
@@ -3820,7 +5362,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B91">
         <f>GETPIVOTDATA("Metric",VarianceP!A1)</f>
@@ -3829,7 +5371,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B92">
         <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","North")</f>
@@ -3838,7 +5380,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B93">
         <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","South")</f>
@@ -3847,7 +5389,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B94">
         <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","West")</f>
@@ -3856,7 +5398,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B95">
         <f>GETPIVOTDATA("Metric",VarianceP!A1,"Product","A")</f>
@@ -3865,7 +5407,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B96">
         <f>GETPIVOTDATA("Metric",VarianceP!A1,"Product","B")</f>
@@ -3874,7 +5416,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B97">
         <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","North","Product","A")</f>
@@ -3883,7 +5425,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B98">
         <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","South","Product","B")</f>
@@ -3892,7 +5434,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B99" t="e">
         <f>GETPIVOTDATA("Metric",VarianceP!A1,"Region","missing")</f>
@@ -3901,7 +5443,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B100" t="e">
         <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Error")</f>
@@ -3910,7 +5452,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B101">
         <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Literal")</f>
@@ -3919,7 +5461,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B102">
         <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Empty")</f>
@@ -3928,7 +5470,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B103">
         <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Single")</f>
@@ -3937,7 +5479,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B104">
         <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","Boolean")</f>
@@ -3946,7 +5488,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B105">
         <f>GETPIVOTDATA("Sum",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -3955,7 +5497,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B106">
         <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Error")</f>
@@ -3964,7 +5506,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B107">
         <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Literal")</f>
@@ -3973,7 +5515,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B108">
         <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Empty")</f>
@@ -3982,7 +5524,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B109">
         <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Single")</f>
@@ -3991,7 +5533,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B110">
         <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","Boolean")</f>
@@ -4000,7 +5542,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B111">
         <f>GETPIVOTDATA("Count",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -4009,7 +5551,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B112">
         <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Error")</f>
@@ -4018,7 +5560,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B113">
         <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Literal")</f>
@@ -4027,7 +5569,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B114">
         <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Empty")</f>
@@ -4036,7 +5578,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B115">
         <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Single")</f>
@@ -4045,7 +5587,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B116">
         <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","Boolean")</f>
@@ -4054,7 +5596,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B117">
         <f>GETPIVOTDATA("CountNumbers",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -4063,7 +5605,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B118" t="e">
         <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Error")</f>
@@ -4072,7 +5614,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B119" t="e">
         <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Literal")</f>
@@ -4081,7 +5623,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B120">
         <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Empty")</f>
@@ -4090,7 +5632,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B121">
         <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Single")</f>
@@ -4099,7 +5641,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B122" t="e">
         <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","Boolean")</f>
@@ -4108,7 +5650,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B123" t="e">
         <f>GETPIVOTDATA("Average",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -4117,7 +5659,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B124" t="e">
         <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Error")</f>
@@ -4126,7 +5668,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B125">
         <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Literal")</f>
@@ -4135,7 +5677,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B126">
         <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Empty")</f>
@@ -4144,7 +5686,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B127">
         <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Single")</f>
@@ -4153,7 +5695,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B128">
         <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","Boolean")</f>
@@ -4162,7 +5704,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B129">
         <f>GETPIVOTDATA("Minimum",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -4171,7 +5713,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B130" t="e">
         <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Error")</f>
@@ -4180,7 +5722,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B131">
         <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Literal")</f>
@@ -4189,7 +5731,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B132">
         <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Empty")</f>
@@ -4198,7 +5740,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B133">
         <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Single")</f>
@@ -4207,7 +5749,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B134">
         <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","Boolean")</f>
@@ -4216,7 +5758,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B135">
         <f>GETPIVOTDATA("Maximum",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -4225,7 +5767,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B136" t="e">
         <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Error")</f>
@@ -4234,7 +5776,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B137">
         <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Literal")</f>
@@ -4243,7 +5785,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B138">
         <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Empty")</f>
@@ -4252,7 +5794,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B139">
         <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Single")</f>
@@ -4261,7 +5803,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B140">
         <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","Boolean")</f>
@@ -4270,7 +5812,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B141">
         <f>GETPIVOTDATA("Product",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -4279,7 +5821,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B142" t="e">
         <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Error")</f>
@@ -4288,7 +5830,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B143" t="e">
         <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Literal")</f>
@@ -4297,7 +5839,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B144">
         <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Empty")</f>
@@ -4306,7 +5848,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B145" t="e">
         <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Single")</f>
@@ -4315,7 +5857,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B146" t="e">
         <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","Boolean")</f>
@@ -4324,7 +5866,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B147" t="e">
         <f>GETPIVOTDATA("StandardDeviation",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -4333,7 +5875,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B148" t="e">
         <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Error")</f>
@@ -4342,7 +5884,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B149" t="e">
         <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Literal")</f>
@@ -4351,7 +5893,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B150">
         <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Empty")</f>
@@ -4360,7 +5902,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B151">
         <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Single")</f>
@@ -4369,7 +5911,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B152" t="e">
         <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","Boolean")</f>
@@ -4378,7 +5920,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B153" t="e">
         <f>GETPIVOTDATA("StandardDeviationP",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -4387,7 +5929,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B154" t="e">
         <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Error")</f>
@@ -4396,7 +5938,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B155" t="e">
         <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Literal")</f>
@@ -4405,7 +5947,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B156">
         <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Empty")</f>
@@ -4414,7 +5956,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B157" t="e">
         <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Single")</f>
@@ -4423,7 +5965,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B158" t="e">
         <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","Boolean")</f>
@@ -4432,7 +5974,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B159" t="e">
         <f>GETPIVOTDATA("Variance",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -4441,7 +5983,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B160" t="e">
         <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Error")</f>
@@ -4450,7 +5992,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B161" t="e">
         <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Literal")</f>
@@ -4459,7 +6001,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B162">
         <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Empty")</f>
@@ -4468,7 +6010,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B163">
         <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Single")</f>
@@ -4477,7 +6019,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B164" t="e">
         <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","Boolean")</f>
@@ -4486,7 +6028,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B165" t="e">
         <f>GETPIVOTDATA("VarianceP",ErrorGroups!A1,"Group","TextNumber")</f>
@@ -4498,8 +6040,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9C61B02-5BDB-4B2E-B689-AACCB895950D}">
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53F0393D-35C8-4CAF-8447-535D92550BE2}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -4631,8 +6173,370 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3BFCC2D-93A0-4D78-91BC-E81BA4D80C56}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55C4BE7A-7FEB-432D-9E3A-AE49C7F22EFE}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F7558A-4C72-4CCA-82F7-42A35F31EB75}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA618899-6FC9-4FA5-AA11-C817244EF819}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA3628A7-C9E0-41DE-840E-56651F909C24}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5366246F-45F7-4092-9111-6DBDA0490FF5}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23E7A9AD-F98A-41A8-B192-729109EEE1A5}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09D8C4CA-9E6D-4931-AD13-7C17F14EE7FC}">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4655,42 +6559,42 @@
         <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1" t="s">
         <v>1</v>
       </c>
       <c r="I1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
@@ -4728,7 +6632,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4744,7 +6648,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="e">
         <v>#N/A</v>
@@ -4782,7 +6686,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
@@ -4820,7 +6724,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
@@ -4858,7 +6762,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
@@ -4930,599 +6834,6 @@
       </c>
       <c r="L8" s="3" t="e">
         <v>#N/A</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F73497-C812-4139-AD85-740CD7E260AE}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="e">
-        <f>NA()</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="str">
-        <f>"#N/A"</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" t="str">
-        <f>"12"</f>
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39E4FC5-3D8F-4C66-90F1-9F156D7F8302}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>36</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>80.888888888888886</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>24.222222222222221</v>
-      </c>
-      <c r="C6" s="3">
-        <v>6.25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>58.64</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2EAD48D-4A6F-4B39-B60E-83C60FE4623D}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>72</v>
-      </c>
-      <c r="C3" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D3" s="3">
-        <v>121.33333333333334</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C4" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D4" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>36.333333333333329</v>
-      </c>
-      <c r="C6" s="3">
-        <v>12.5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>73.3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A92727-DD3B-490C-9C6C-44E23A1A7EAE}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>8.9938250421546933</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>4.9216076867444665</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>7.657675887630659</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDDF8AB1-9FE2-46CF-909D-C5222AAE4748}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>8.4852813742385695</v>
-      </c>
-      <c r="C3" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D3" s="3">
-        <v>11.015141094572204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C4" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D4" s="3">
-        <v>7.0710678118654755</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>6.0277137733417074</v>
-      </c>
-      <c r="C6" s="3">
-        <v>3.5355339059327378</v>
-      </c>
-      <c r="D6" s="3">
-        <v>8.5615419172015965</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2718F54-D9D0-470A-A622-1AC866A99400}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>-20</v>
-      </c>
-      <c r="C3" s="3">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>-100</v>
-      </c>
-      <c r="C6" s="3">
-        <v>300</v>
-      </c>
-      <c r="D6" s="3">
-        <v>-30000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F48E771-E57D-4C48-9B8A-913F87123E4C}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
